--- a/compare/output/dscale_energy_intensity_downscaled_SSP126.xlsx
+++ b/compare/output/dscale_energy_intensity_downscaled_SSP126.xlsx
@@ -4478,58 +4478,58 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1884.84161284911</v>
+        <v>3588.50999273397</v>
       </c>
       <c r="F54" t="n">
-        <v>1959.725555155978</v>
+        <v>3727.522275385561</v>
       </c>
       <c r="G54" t="n">
-        <v>1730.073225353299</v>
+        <v>3275.106928297146</v>
       </c>
       <c r="H54" t="n">
-        <v>1532.100213955683</v>
+        <v>2880.932952753813</v>
       </c>
       <c r="I54" t="n">
-        <v>1394.636743382498</v>
+        <v>2601.859043371897</v>
       </c>
       <c r="J54" t="n">
-        <v>1293.373184766094</v>
+        <v>2391.604929461661</v>
       </c>
       <c r="K54" t="n">
-        <v>1317.10096910642</v>
+        <v>2232.191580358568</v>
       </c>
       <c r="L54" t="n">
-        <v>1334.713778532337</v>
+        <v>2107.605919276607</v>
       </c>
       <c r="M54" t="n">
-        <v>1345.211536699385</v>
+        <v>2003.772202130948</v>
       </c>
       <c r="N54" t="n">
-        <v>1344.309169268567</v>
+        <v>1907.093770529539</v>
       </c>
       <c r="O54" t="n">
-        <v>1330.473350031392</v>
+        <v>1812.513963688593</v>
       </c>
       <c r="P54" t="n">
-        <v>1311.359127671395</v>
+        <v>1726.485897970159</v>
       </c>
       <c r="Q54" t="n">
-        <v>1288.278927239425</v>
+        <v>1646.634686281107</v>
       </c>
       <c r="R54" t="n">
-        <v>1260.032945740836</v>
+        <v>1570.129495757475</v>
       </c>
       <c r="S54" t="n">
-        <v>1227.322744330903</v>
+        <v>1495.453356212595</v>
       </c>
       <c r="T54" t="n">
-        <v>1192.418017923313</v>
+        <v>1424.08770999308</v>
       </c>
       <c r="U54" t="n">
-        <v>1156.419085821251</v>
+        <v>1356.518429437511</v>
       </c>
       <c r="V54" t="n">
-        <v>1119.422675958509</v>
+        <v>1292.152731495302</v>
       </c>
     </row>
     <row r="55">
@@ -4554,58 +4554,58 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>18787.86273390986</v>
+        <v>5034.111308450916</v>
       </c>
       <c r="F55" t="n">
-        <v>20624.61528933098</v>
+        <v>5283.364859168042</v>
       </c>
       <c r="G55" t="n">
-        <v>18841.40315109186</v>
+        <v>4688.88112032345</v>
       </c>
       <c r="H55" t="n">
-        <v>16987.8113640952</v>
+        <v>4158.915073331329</v>
       </c>
       <c r="I55" t="n">
-        <v>15559.18290207219</v>
+        <v>3779.746292127457</v>
       </c>
       <c r="J55" t="n">
-        <v>14386.18475987872</v>
+        <v>3489.148636586204</v>
       </c>
       <c r="K55" t="n">
-        <v>12438.27050263772</v>
+        <v>3264.401498714069</v>
       </c>
       <c r="L55" t="n">
-        <v>10877.2153771543</v>
+        <v>3084.686181412763</v>
       </c>
       <c r="M55" t="n">
-        <v>9587.531364983566</v>
+        <v>2931.235251894489</v>
       </c>
       <c r="N55" t="n">
-        <v>8471.943188135028</v>
+        <v>2785.257696428562</v>
       </c>
       <c r="O55" t="n">
-        <v>7493.256783213756</v>
+        <v>2641.256433406385</v>
       </c>
       <c r="P55" t="n">
-        <v>6653.704215909543</v>
+        <v>2508.560639492868</v>
       </c>
       <c r="Q55" t="n">
-        <v>5918.859117733114</v>
+        <v>2382.807512777722</v>
       </c>
       <c r="R55" t="n">
-        <v>5272.337692200809</v>
+        <v>2261.407078510214</v>
       </c>
       <c r="S55" t="n">
-        <v>4694.861570640717</v>
+        <v>2141.526537074698</v>
       </c>
       <c r="T55" t="n">
-        <v>4184.99092884256</v>
+        <v>2025.940110032163</v>
       </c>
       <c r="U55" t="n">
-        <v>3741.267348742279</v>
+        <v>1916.659976135317</v>
       </c>
       <c r="V55" t="n">
-        <v>3355.255207594228</v>
+        <v>1813.414102472654</v>
       </c>
     </row>
     <row r="56">
@@ -6910,58 +6910,58 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>9028.889385758499</v>
+        <v>4659.60228288571</v>
       </c>
       <c r="F86" t="n">
-        <v>8565.013322126466</v>
+        <v>4351.278335136853</v>
       </c>
       <c r="G86" t="n">
-        <v>7956.635629476942</v>
+        <v>4017.2922822782</v>
       </c>
       <c r="H86" t="n">
-        <v>7347.315448898184</v>
+        <v>3729.182812603658</v>
       </c>
       <c r="I86" t="n">
-        <v>6895.718321624207</v>
+        <v>3542.20108195005</v>
       </c>
       <c r="J86" t="n">
-        <v>6474.389122682387</v>
+        <v>3370.217000777926</v>
       </c>
       <c r="K86" t="n">
-        <v>6081.645236912163</v>
+        <v>3201.451748025936</v>
       </c>
       <c r="L86" t="n">
-        <v>5722.655772584607</v>
+        <v>3039.814175960076</v>
       </c>
       <c r="M86" t="n">
-        <v>5383.849341382134</v>
+        <v>2882.825803410386</v>
       </c>
       <c r="N86" t="n">
-        <v>5045.091123576914</v>
+        <v>2721.40166132937</v>
       </c>
       <c r="O86" t="n">
-        <v>4695.552466894179</v>
+        <v>2549.577597434306</v>
       </c>
       <c r="P86" t="n">
-        <v>4352.729824389203</v>
+        <v>2377.70043877772</v>
       </c>
       <c r="Q86" t="n">
-        <v>4027.78895590591</v>
+        <v>2212.431145588231</v>
       </c>
       <c r="R86" t="n">
-        <v>3720.878701673822</v>
+        <v>2055.673564705593</v>
       </c>
       <c r="S86" t="n">
-        <v>3440.406386070064</v>
+        <v>1912.735578540549</v>
       </c>
       <c r="T86" t="n">
-        <v>3179.685444306132</v>
+        <v>1779.479780483626</v>
       </c>
       <c r="U86" t="n">
-        <v>2940.475114306669</v>
+        <v>1654.939845796793</v>
       </c>
       <c r="V86" t="n">
-        <v>2724.870320459009</v>
+        <v>1540.414944252605</v>
       </c>
     </row>
     <row r="87">
@@ -6986,58 +6986,58 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5035.884972882833</v>
+        <v>2598.904484640586</v>
       </c>
       <c r="F87" t="n">
-        <v>4784.27538603809</v>
+        <v>2430.552417574775</v>
       </c>
       <c r="G87" t="n">
-        <v>4440.628992109064</v>
+        <v>2242.066296515941</v>
       </c>
       <c r="H87" t="n">
-        <v>4096.020188718092</v>
+        <v>2078.964513520653</v>
       </c>
       <c r="I87" t="n">
-        <v>3840.989229516844</v>
+        <v>1973.044078942694</v>
       </c>
       <c r="J87" t="n">
-        <v>3604.038964395943</v>
+        <v>1876.067866654191</v>
       </c>
       <c r="K87" t="n">
-        <v>3383.917029868121</v>
+        <v>1781.334929684723</v>
       </c>
       <c r="L87" t="n">
-        <v>3182.806092745395</v>
+        <v>1690.672908617209</v>
       </c>
       <c r="M87" t="n">
-        <v>2992.348359754683</v>
+        <v>1602.277203043289</v>
       </c>
       <c r="N87" t="n">
-        <v>2800.866055136682</v>
+        <v>1510.831291029449</v>
       </c>
       <c r="O87" t="n">
-        <v>2603.644932080563</v>
+        <v>1413.719650092673</v>
       </c>
       <c r="P87" t="n">
-        <v>2412.035807682566</v>
+        <v>1317.586624863612</v>
       </c>
       <c r="Q87" t="n">
-        <v>2232.193196309831</v>
+        <v>1226.125252476123</v>
       </c>
       <c r="R87" t="n">
-        <v>2063.943872312176</v>
+        <v>1140.266909383568</v>
       </c>
       <c r="S87" t="n">
-        <v>1911.276638028941</v>
+        <v>1062.597384072743</v>
       </c>
       <c r="T87" t="n">
-        <v>1770.232848807719</v>
+        <v>990.6934558044042</v>
       </c>
       <c r="U87" t="n">
-        <v>1641.184749804471</v>
+        <v>923.6813546033702</v>
       </c>
       <c r="V87" t="n">
-        <v>1524.797988899958</v>
+        <v>861.9939053420677</v>
       </c>
     </row>
     <row r="88">
@@ -7062,58 +7062,58 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>8678.289561851798</v>
+        <v>4478.665772308495</v>
       </c>
       <c r="F88" t="n">
-        <v>8211.079759456141</v>
+        <v>4171.469689733125</v>
       </c>
       <c r="G88" t="n">
-        <v>7633.093462168692</v>
+        <v>3853.936372541962</v>
       </c>
       <c r="H88" t="n">
-        <v>7055.652400034948</v>
+        <v>3581.14713392981</v>
       </c>
       <c r="I88" t="n">
-        <v>6622.137932968258</v>
+        <v>3401.667970892668</v>
       </c>
       <c r="J88" t="n">
-        <v>6211.467700134147</v>
+        <v>3233.354320553578</v>
       </c>
       <c r="K88" t="n">
-        <v>5826.739310801465</v>
+        <v>3067.266179658972</v>
       </c>
       <c r="L88" t="n">
-        <v>5474.61786219789</v>
+        <v>2908.059063275378</v>
       </c>
       <c r="M88" t="n">
-        <v>5140.449260817682</v>
+        <v>2752.495255816875</v>
       </c>
       <c r="N88" t="n">
-        <v>4802.989627682995</v>
+        <v>2590.808298988382</v>
       </c>
       <c r="O88" t="n">
-        <v>4454.004077874827</v>
+        <v>2418.422346660249</v>
       </c>
       <c r="P88" t="n">
-        <v>4114.044952735797</v>
+        <v>2247.317633742246</v>
       </c>
       <c r="Q88" t="n">
-        <v>3795.438832143427</v>
+        <v>2084.803145184148</v>
       </c>
       <c r="R88" t="n">
-        <v>3497.872554833498</v>
+        <v>1932.46937623564</v>
       </c>
       <c r="S88" t="n">
-        <v>3228.588425883355</v>
+        <v>1794.972819389344</v>
       </c>
       <c r="T88" t="n">
-        <v>2979.741386859512</v>
+        <v>1667.583049286412</v>
       </c>
       <c r="U88" t="n">
-        <v>2751.057494467061</v>
+        <v>1548.333003575363</v>
       </c>
       <c r="V88" t="n">
-        <v>2543.858041968554</v>
+        <v>1438.085663926566</v>
       </c>
     </row>
     <row r="89">
@@ -7138,58 +7138,58 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>10255.26989478915</v>
+        <v>5292.509075205979</v>
       </c>
       <c r="F89" t="n">
-        <v>9691.821908925021</v>
+        <v>4923.730193322876</v>
       </c>
       <c r="G89" t="n">
-        <v>8975.549477515195</v>
+        <v>4531.740213371507</v>
       </c>
       <c r="H89" t="n">
-        <v>8265.17946673846</v>
+        <v>4195.051297958269</v>
       </c>
       <c r="I89" t="n">
-        <v>7737.295398627038</v>
+        <v>3974.503431569211</v>
       </c>
       <c r="J89" t="n">
-        <v>7249.179064337016</v>
+        <v>3773.530762737609</v>
       </c>
       <c r="K89" t="n">
-        <v>6798.312346043643</v>
+        <v>3578.713998600917</v>
       </c>
       <c r="L89" t="n">
-        <v>6386.931689120479</v>
+        <v>3392.670511907565</v>
       </c>
       <c r="M89" t="n">
-        <v>5994.933179521259</v>
+        <v>3210.035601623009</v>
       </c>
       <c r="N89" t="n">
-        <v>5597.953855141413</v>
+        <v>3019.624531688231</v>
       </c>
       <c r="O89" t="n">
-        <v>5187.976965908058</v>
+        <v>2816.952838148187</v>
       </c>
       <c r="P89" t="n">
-        <v>4789.122037321498</v>
+        <v>2616.081867904234</v>
       </c>
       <c r="Q89" t="n">
-        <v>4415.331637199683</v>
+        <v>2425.305133703641</v>
       </c>
       <c r="R89" t="n">
-        <v>4065.814243462654</v>
+        <v>2246.240076440465</v>
       </c>
       <c r="S89" t="n">
-        <v>3747.297556243681</v>
+        <v>2083.35543970685</v>
       </c>
       <c r="T89" t="n">
-        <v>3452.793521261119</v>
+        <v>1932.322037786477</v>
       </c>
       <c r="U89" t="n">
-        <v>3183.872533047376</v>
+        <v>1791.92726143475</v>
       </c>
       <c r="V89" t="n">
-        <v>2941.63869220482</v>
+        <v>1662.957744463335</v>
       </c>
     </row>
     <row r="90">
@@ -7214,58 +7214,58 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>153.8562413281299</v>
+        <v>4810.633561287933</v>
       </c>
       <c r="F90" t="n">
-        <v>262.9082037009251</v>
+        <v>4479.218860341331</v>
       </c>
       <c r="G90" t="n">
-        <v>327.5179735349554</v>
+        <v>4122.98947520052</v>
       </c>
       <c r="H90" t="n">
-        <v>367.6998854015351</v>
+        <v>3814.689462521213</v>
       </c>
       <c r="I90" t="n">
-        <v>401.6361140629194</v>
+        <v>3610.996193432337</v>
       </c>
       <c r="J90" t="n">
-        <v>429.0437698010848</v>
+        <v>3424.527022036442</v>
       </c>
       <c r="K90" t="n">
-        <v>450.0450549222766</v>
+        <v>3242.846171097569</v>
       </c>
       <c r="L90" t="n">
-        <v>465.4592745988643</v>
+        <v>3069.181959366394</v>
       </c>
       <c r="M90" t="n">
-        <v>473.8449504577181</v>
+        <v>2900.004603858239</v>
       </c>
       <c r="N90" t="n">
-        <v>474.2329512342553</v>
+        <v>2725.95077967885</v>
       </c>
       <c r="O90" t="n">
-        <v>466.3686298000623</v>
+        <v>2542.370741854458</v>
       </c>
       <c r="P90" t="n">
-        <v>453.5943921143021</v>
+        <v>2361.123296348112</v>
       </c>
       <c r="Q90" t="n">
-        <v>438.6267460374614</v>
+        <v>2189.373128638255</v>
       </c>
       <c r="R90" t="n">
-        <v>422.6486148137317</v>
+        <v>2028.667229281945</v>
       </c>
       <c r="S90" t="n">
-        <v>407.0564551059997</v>
+        <v>1883.30198196974</v>
       </c>
       <c r="T90" t="n">
-        <v>390.5587545771248</v>
+        <v>1748.46822320699</v>
       </c>
       <c r="U90" t="n">
-        <v>374.2299912195029</v>
+        <v>1622.812120870547</v>
       </c>
       <c r="V90" t="n">
-        <v>358.9050064640615</v>
+        <v>1507.386160677282</v>
       </c>
     </row>
     <row r="91">
@@ -7290,58 +7290,58 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>9309.804318637711</v>
+        <v>4804.576022919798</v>
       </c>
       <c r="F91" t="n">
-        <v>8801.695601467072</v>
+        <v>4471.519884764273</v>
       </c>
       <c r="G91" t="n">
-        <v>8152.795363722941</v>
+        <v>4116.333010439863</v>
       </c>
       <c r="H91" t="n">
-        <v>7513.208963383816</v>
+        <v>3813.383259315443</v>
       </c>
       <c r="I91" t="n">
-        <v>7043.587165512489</v>
+        <v>3618.158531835097</v>
       </c>
       <c r="J91" t="n">
-        <v>6611.676893985506</v>
+        <v>3441.681593351256</v>
       </c>
       <c r="K91" t="n">
-        <v>6213.050239959409</v>
+        <v>3270.624933955228</v>
       </c>
       <c r="L91" t="n">
-        <v>5848.98344542452</v>
+        <v>3106.918098681644</v>
       </c>
       <c r="M91" t="n">
-        <v>5500.774515652213</v>
+        <v>2945.434336465126</v>
       </c>
       <c r="N91" t="n">
-        <v>5144.897626439024</v>
+        <v>2775.238861892913</v>
       </c>
       <c r="O91" t="n">
-        <v>4774.137067373299</v>
+        <v>2592.247238184154</v>
       </c>
       <c r="P91" t="n">
-        <v>4411.200595985649</v>
+        <v>2409.640390227552</v>
       </c>
       <c r="Q91" t="n">
-        <v>4070.083157509157</v>
+        <v>2235.663000569552</v>
       </c>
       <c r="R91" t="n">
-        <v>3750.891146268036</v>
+        <v>2072.254537614544</v>
       </c>
       <c r="S91" t="n">
-        <v>3459.680623706643</v>
+        <v>1923.451324275939</v>
       </c>
       <c r="T91" t="n">
-        <v>3190.080765245079</v>
+        <v>1785.29741991656</v>
       </c>
       <c r="U91" t="n">
-        <v>2943.894137075056</v>
+        <v>1656.864118847699</v>
       </c>
       <c r="V91" t="n">
-        <v>2722.325142124864</v>
+        <v>1538.97611220708</v>
       </c>
     </row>
     <row r="92">
@@ -7366,58 +7366,58 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>10057.47930951333</v>
+        <v>5190.433900389669</v>
       </c>
       <c r="F92" t="n">
-        <v>9508.333544272244</v>
+        <v>4830.512714749291</v>
       </c>
       <c r="G92" t="n">
-        <v>8796.821784574293</v>
+        <v>4441.50089427128</v>
       </c>
       <c r="H92" t="n">
-        <v>8094.429774354231</v>
+        <v>4108.386063226132</v>
       </c>
       <c r="I92" t="n">
-        <v>7576.458114645176</v>
+        <v>3891.884337391286</v>
       </c>
       <c r="J92" t="n">
-        <v>7100.50229003369</v>
+        <v>3696.137670831101</v>
       </c>
       <c r="K92" t="n">
-        <v>6661.557187952127</v>
+        <v>3506.724426228982</v>
       </c>
       <c r="L92" t="n">
-        <v>6261.768801643594</v>
+        <v>3326.185310856635</v>
       </c>
       <c r="M92" t="n">
-        <v>5880.755482246195</v>
+        <v>3148.898227416964</v>
       </c>
       <c r="N92" t="n">
-        <v>5494.709810903882</v>
+        <v>2963.933067136817</v>
       </c>
       <c r="O92" t="n">
-        <v>5095.36258923182</v>
+        <v>2766.665349801812</v>
       </c>
       <c r="P92" t="n">
-        <v>4705.995344470381</v>
+        <v>2570.673496146551</v>
       </c>
       <c r="Q92" t="n">
-        <v>4340.241278657466</v>
+        <v>2384.058621099166</v>
       </c>
       <c r="R92" t="n">
-        <v>3998.009890619144</v>
+        <v>2208.780210935382</v>
       </c>
       <c r="S92" t="n">
-        <v>3686.652067759896</v>
+        <v>2049.638846225992</v>
       </c>
       <c r="T92" t="n">
-        <v>3398.95218664757</v>
+        <v>1902.190262822711</v>
       </c>
       <c r="U92" t="n">
-        <v>3136.896556482231</v>
+        <v>1765.488535578859</v>
       </c>
       <c r="V92" t="n">
-        <v>2900.745827014971</v>
+        <v>1639.840321157383</v>
       </c>
     </row>
     <row r="93">
@@ -7442,58 +7442,58 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4126.648896907098</v>
+        <v>2129.668644629646</v>
       </c>
       <c r="F93" t="n">
-        <v>3932.727091934553</v>
+        <v>1997.940872837997</v>
       </c>
       <c r="G93" t="n">
-        <v>3657.123362405856</v>
+        <v>1846.475588816912</v>
       </c>
       <c r="H93" t="n">
-        <v>3373.129175509263</v>
+        <v>1712.055979262911</v>
       </c>
       <c r="I93" t="n">
-        <v>3158.9830140743</v>
+        <v>1622.710286056662</v>
       </c>
       <c r="J93" t="n">
-        <v>2959.23968166845</v>
+        <v>1540.420215022061</v>
       </c>
       <c r="K93" t="n">
-        <v>2774.658526289972</v>
+        <v>1460.613870616369</v>
       </c>
       <c r="L93" t="n">
-        <v>2607.616762551756</v>
+        <v>1385.138424415929</v>
       </c>
       <c r="M93" t="n">
-        <v>2451.519656889368</v>
+        <v>1312.686086900783</v>
       </c>
       <c r="N93" t="n">
-        <v>2296.207727277746</v>
+        <v>1238.610635722223</v>
       </c>
       <c r="O93" t="n">
-        <v>2136.898733396089</v>
+        <v>1160.287139158486</v>
       </c>
       <c r="P93" t="n">
-        <v>1981.892885051823</v>
+        <v>1082.618901803315</v>
       </c>
       <c r="Q93" t="n">
-        <v>1835.621386355758</v>
+        <v>1008.29163869807</v>
       </c>
       <c r="R93" t="n">
-        <v>1698.361538393696</v>
+        <v>938.2936659958754</v>
       </c>
       <c r="S93" t="n">
-        <v>1574.049336216757</v>
+        <v>875.1117832921849</v>
       </c>
       <c r="T93" t="n">
-        <v>1459.272375585551</v>
+        <v>816.6674760826219</v>
       </c>
       <c r="U93" t="n">
-        <v>1354.240640564912</v>
+        <v>762.1852625192306</v>
       </c>
       <c r="V93" t="n">
-        <v>1259.353549816389</v>
+        <v>711.9337069565212</v>
       </c>
     </row>
     <row r="94">
@@ -7518,58 +7518,58 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>141.1116216946559</v>
+        <v>3960.072586656939</v>
       </c>
       <c r="F94" t="n">
-        <v>224.976472768838</v>
+        <v>3684.746252514935</v>
       </c>
       <c r="G94" t="n">
-        <v>278.4464713258679</v>
+        <v>3392.229723720181</v>
       </c>
       <c r="H94" t="n">
-        <v>318.2800057890467</v>
+        <v>3142.412155644813</v>
       </c>
       <c r="I94" t="n">
-        <v>355.8518214439954</v>
+        <v>2980.13110221643</v>
       </c>
       <c r="J94" t="n">
-        <v>386.632263460713</v>
+        <v>2831.403592882154</v>
       </c>
       <c r="K94" t="n">
-        <v>410.3052268362679</v>
+        <v>2685.710686229433</v>
       </c>
       <c r="L94" t="n">
-        <v>428.5595281647462</v>
+        <v>2546.188573547068</v>
       </c>
       <c r="M94" t="n">
-        <v>441.0118309515874</v>
+        <v>2410.365439725465</v>
       </c>
       <c r="N94" t="n">
-        <v>445.8329672670816</v>
+        <v>2269.993541024008</v>
       </c>
       <c r="O94" t="n">
-        <v>442.2207409957662</v>
+        <v>2120.908737038489</v>
       </c>
       <c r="P94" t="n">
-        <v>433.1704213475397</v>
+        <v>1972.976210211819</v>
       </c>
       <c r="Q94" t="n">
-        <v>421.6837409358407</v>
+        <v>1832.492947232103</v>
       </c>
       <c r="R94" t="n">
-        <v>409.0051302275084</v>
+        <v>1700.897697362313</v>
       </c>
       <c r="S94" t="n">
-        <v>396.7942181432833</v>
+        <v>1582.012649575086</v>
       </c>
       <c r="T94" t="n">
-        <v>384.8778277395655</v>
+        <v>1472.377517881171</v>
       </c>
       <c r="U94" t="n">
-        <v>372.8827780613379</v>
+        <v>1370.139432093582</v>
       </c>
       <c r="V94" t="n">
-        <v>360.6470758080031</v>
+        <v>1275.668512289204</v>
       </c>
     </row>
     <row r="95">
@@ -7594,58 +7594,58 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>7671.307129370642</v>
+        <v>3958.985284406586</v>
       </c>
       <c r="F95" t="n">
-        <v>7288.717541197626</v>
+        <v>3702.882591674535</v>
       </c>
       <c r="G95" t="n">
-        <v>6763.833887608445</v>
+        <v>3415.048638730139</v>
       </c>
       <c r="H95" t="n">
-        <v>6236.482530582201</v>
+        <v>3165.371573590818</v>
       </c>
       <c r="I95" t="n">
-        <v>5845.328739269427</v>
+        <v>3002.635667360496</v>
       </c>
       <c r="J95" t="n">
-        <v>5483.524191012324</v>
+        <v>2854.426279072798</v>
       </c>
       <c r="K95" t="n">
-        <v>5148.849152549951</v>
+        <v>2710.416585911959</v>
       </c>
       <c r="L95" t="n">
-        <v>4844.082855528914</v>
+        <v>2573.125541517568</v>
       </c>
       <c r="M95" t="n">
-        <v>4554.344899508626</v>
+        <v>2438.660921100013</v>
       </c>
       <c r="N95" t="n">
-        <v>4260.938489583645</v>
+        <v>2298.417372518583</v>
       </c>
       <c r="O95" t="n">
-        <v>3956.837823279195</v>
+        <v>2148.472441114013</v>
       </c>
       <c r="P95" t="n">
-        <v>3659.395552184048</v>
+        <v>1998.963124550478</v>
       </c>
       <c r="Q95" t="n">
-        <v>3380.103696155207</v>
+        <v>1856.662991671058</v>
       </c>
       <c r="R95" t="n">
-        <v>3118.846446050852</v>
+        <v>1723.068851621161</v>
       </c>
       <c r="S95" t="n">
-        <v>2881.859633563068</v>
+        <v>1602.204749936865</v>
       </c>
       <c r="T95" t="n">
-        <v>2661.643721937236</v>
+        <v>1489.562810220625</v>
       </c>
       <c r="U95" t="n">
-        <v>2460.475756857795</v>
+        <v>1384.789604181297</v>
       </c>
       <c r="V95" t="n">
-        <v>2278.265649796419</v>
+        <v>1287.941825187013</v>
       </c>
     </row>
     <row r="96">
@@ -7670,58 +7670,58 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>7516.585726680722</v>
+        <v>3879.137124746585</v>
       </c>
       <c r="F96" t="n">
-        <v>7122.376191574942</v>
+        <v>3618.376300363637</v>
       </c>
       <c r="G96" t="n">
-        <v>6631.831073966556</v>
+        <v>3348.400634574901</v>
       </c>
       <c r="H96" t="n">
-        <v>6141.870750491975</v>
+        <v>3117.3506839719</v>
       </c>
       <c r="I96" t="n">
-        <v>5776.325333429336</v>
+        <v>2967.189912848253</v>
       </c>
       <c r="J96" t="n">
-        <v>5428.273403090347</v>
+        <v>2825.665705489952</v>
       </c>
       <c r="K96" t="n">
-        <v>5100.25537817084</v>
+        <v>2684.836234236682</v>
       </c>
       <c r="L96" t="n">
-        <v>4798.631334406972</v>
+        <v>2548.982174573474</v>
       </c>
       <c r="M96" t="n">
-        <v>4511.592119323201</v>
+        <v>2415.768598142583</v>
       </c>
       <c r="N96" t="n">
-        <v>4220.687506505102</v>
+        <v>2276.705357903834</v>
       </c>
       <c r="O96" t="n">
-        <v>3918.460356603242</v>
+        <v>2127.634354440619</v>
       </c>
       <c r="P96" t="n">
-        <v>3622.804025330506</v>
+        <v>1978.974819975888</v>
       </c>
       <c r="Q96" t="n">
-        <v>3344.98426417752</v>
+        <v>1837.372178283277</v>
       </c>
       <c r="R96" t="n">
-        <v>3085.445623426661</v>
+        <v>1704.615901764448</v>
       </c>
       <c r="S96" t="n">
-        <v>2849.551559545961</v>
+        <v>1584.242685079033</v>
       </c>
       <c r="T96" t="n">
-        <v>2631.840476305287</v>
+        <v>1472.883716040457</v>
       </c>
       <c r="U96" t="n">
-        <v>2432.404539982066</v>
+        <v>1368.990737153779</v>
       </c>
       <c r="V96" t="n">
-        <v>2251.918425095222</v>
+        <v>1273.047296678723</v>
       </c>
     </row>
     <row r="97">
@@ -7746,58 +7746,58 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>8185.992085327922</v>
+        <v>4224.602360142794</v>
       </c>
       <c r="F97" t="n">
-        <v>7752.571760650189</v>
+        <v>3938.534159264498</v>
       </c>
       <c r="G97" t="n">
-        <v>7215.963393057936</v>
+        <v>3643.328084647751</v>
       </c>
       <c r="H97" t="n">
-        <v>6678.130374822021</v>
+        <v>3389.533114134859</v>
       </c>
       <c r="I97" t="n">
-        <v>6273.963274041467</v>
+        <v>3222.81718319626</v>
       </c>
       <c r="J97" t="n">
-        <v>5889.769174123359</v>
+        <v>3065.895457492393</v>
       </c>
       <c r="K97" t="n">
-        <v>5529.035371020964</v>
+        <v>2910.5512182846</v>
       </c>
       <c r="L97" t="n">
-        <v>5198.278905990688</v>
+        <v>2761.270734604142</v>
       </c>
       <c r="M97" t="n">
-        <v>4883.839663379531</v>
+        <v>2615.091565263894</v>
       </c>
       <c r="N97" t="n">
-        <v>4566.006590123863</v>
+        <v>2462.975913739406</v>
       </c>
       <c r="O97" t="n">
-        <v>4237.17042380391</v>
+        <v>2300.686631703336</v>
       </c>
       <c r="P97" t="n">
-        <v>3916.644563322673</v>
+        <v>2139.486683636298</v>
       </c>
       <c r="Q97" t="n">
-        <v>3615.024586886756</v>
+        <v>1985.703093097845</v>
       </c>
       <c r="R97" t="n">
-        <v>3332.3245237898</v>
+        <v>1841.009068496744</v>
       </c>
       <c r="S97" t="n">
-        <v>3075.168811711401</v>
+        <v>1709.677327654372</v>
       </c>
       <c r="T97" t="n">
-        <v>2837.544220730339</v>
+        <v>1588.003799581178</v>
       </c>
       <c r="U97" t="n">
-        <v>2619.593023782064</v>
+        <v>1474.342990947787</v>
       </c>
       <c r="V97" t="n">
-        <v>2422.6463382277</v>
+        <v>1369.562652592814</v>
       </c>
     </row>
     <row r="98">
@@ -7822,58 +7822,58 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1466.212888400747</v>
+        <v>3831.195187628814</v>
       </c>
       <c r="F98" t="n">
-        <v>1507.556736810886</v>
+        <v>3608.31065210229</v>
       </c>
       <c r="G98" t="n">
-        <v>1464.684227295757</v>
+        <v>3150.242299178941</v>
       </c>
       <c r="H98" t="n">
-        <v>1388.076203791847</v>
+        <v>2737.432924027289</v>
       </c>
       <c r="I98" t="n">
-        <v>1311.174379352847</v>
+        <v>2431.806881278897</v>
       </c>
       <c r="J98" t="n">
-        <v>1236.412592445741</v>
+        <v>2206.373531563908</v>
       </c>
       <c r="K98" t="n">
-        <v>1270.463012965953</v>
+        <v>2035.393764142631</v>
       </c>
       <c r="L98" t="n">
-        <v>1285.197212894202</v>
+        <v>1896.075147278352</v>
       </c>
       <c r="M98" t="n">
-        <v>1283.562991511868</v>
+        <v>1774.193391070546</v>
       </c>
       <c r="N98" t="n">
-        <v>1267.46392430195</v>
+        <v>1662.11105933311</v>
       </c>
       <c r="O98" t="n">
-        <v>1239.096044175034</v>
+        <v>1556.011014776484</v>
       </c>
       <c r="P98" t="n">
-        <v>1205.13274596413</v>
+        <v>1459.257831202011</v>
       </c>
       <c r="Q98" t="n">
-        <v>1170.551112580352</v>
+        <v>1373.039477933834</v>
       </c>
       <c r="R98" t="n">
-        <v>1132.198149023359</v>
+        <v>1291.895006701329</v>
       </c>
       <c r="S98" t="n">
-        <v>1088.565896161628</v>
+        <v>1213.129966289453</v>
       </c>
       <c r="T98" t="n">
-        <v>1043.186779281532</v>
+        <v>1138.318793135903</v>
       </c>
       <c r="U98" t="n">
-        <v>997.4365469094561</v>
+        <v>1068.417391173353</v>
       </c>
       <c r="V98" t="n">
-        <v>952.2647319101922</v>
+        <v>1003.590334789744</v>
       </c>
     </row>
     <row r="99">
@@ -7898,58 +7898,58 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1465.842144638986</v>
+        <v>4493.301415708549</v>
       </c>
       <c r="F99" t="n">
-        <v>1305.012524492073</v>
+        <v>4176.956538493595</v>
       </c>
       <c r="G99" t="n">
-        <v>1079.57128407588</v>
+        <v>3575.393933597012</v>
       </c>
       <c r="H99" t="n">
-        <v>904.7295294412614</v>
+        <v>3043.236899242648</v>
       </c>
       <c r="I99" t="n">
-        <v>787.1891828607625</v>
+        <v>2653.226989988957</v>
       </c>
       <c r="J99" t="n">
-        <v>707.8089492534157</v>
+        <v>2369.826328744483</v>
       </c>
       <c r="K99" t="n">
-        <v>709.6117001146752</v>
+        <v>2158.114351764529</v>
       </c>
       <c r="L99" t="n">
-        <v>710.3010914354189</v>
+        <v>1988.864526124224</v>
       </c>
       <c r="M99" t="n">
-        <v>707.5018412665478</v>
+        <v>1844.06199214336</v>
       </c>
       <c r="N99" t="n">
-        <v>699.6590072609765</v>
+        <v>1713.857966558662</v>
       </c>
       <c r="O99" t="n">
-        <v>686.7020827548787</v>
+        <v>1593.324737380815</v>
       </c>
       <c r="P99" t="n">
-        <v>670.7548622854737</v>
+        <v>1484.68580397719</v>
       </c>
       <c r="Q99" t="n">
-        <v>653.8236748075284</v>
+        <v>1388.187316680556</v>
       </c>
       <c r="R99" t="n">
-        <v>634.9787123496934</v>
+        <v>1298.473417227164</v>
       </c>
       <c r="S99" t="n">
-        <v>614.3072537750631</v>
+        <v>1213.325461009668</v>
       </c>
       <c r="T99" t="n">
-        <v>591.5944756692259</v>
+        <v>1133.006263522887</v>
       </c>
       <c r="U99" t="n">
-        <v>568.0087414044226</v>
+        <v>1058.314263873169</v>
       </c>
       <c r="V99" t="n">
-        <v>544.6624971132194</v>
+        <v>989.4983705971688</v>
       </c>
     </row>
     <row r="100">
@@ -7974,58 +7974,58 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1685.086225817353</v>
+        <v>3323.347884991801</v>
       </c>
       <c r="F100" t="n">
-        <v>1763.598548158762</v>
+        <v>3170.211333113027</v>
       </c>
       <c r="G100" t="n">
-        <v>1701.509604375892</v>
+        <v>2795.85819773406</v>
       </c>
       <c r="H100" t="n">
-        <v>1594.226422634422</v>
+        <v>2448.126110338108</v>
       </c>
       <c r="I100" t="n">
-        <v>1489.892443599801</v>
+        <v>2187.517047541459</v>
       </c>
       <c r="J100" t="n">
-        <v>1394.565901628105</v>
+        <v>1994.439776393637</v>
       </c>
       <c r="K100" t="n">
-        <v>1425.224267073034</v>
+        <v>1847.611211961988</v>
       </c>
       <c r="L100" t="n">
-        <v>1437.565931601388</v>
+        <v>1728.060584314485</v>
       </c>
       <c r="M100" t="n">
-        <v>1433.852281719462</v>
+        <v>1623.233444181632</v>
       </c>
       <c r="N100" t="n">
-        <v>1414.131758076106</v>
+        <v>1525.959282379251</v>
       </c>
       <c r="O100" t="n">
-        <v>1379.95650478496</v>
+        <v>1432.70164404333</v>
       </c>
       <c r="P100" t="n">
-        <v>1338.009538094259</v>
+        <v>1346.618410172316</v>
       </c>
       <c r="Q100" t="n">
-        <v>1292.457444461648</v>
+        <v>1268.649817762866</v>
       </c>
       <c r="R100" t="n">
-        <v>1241.633028712801</v>
+        <v>1194.336290682411</v>
       </c>
       <c r="S100" t="n">
-        <v>1188.792698532502</v>
+        <v>1122.695684454885</v>
       </c>
       <c r="T100" t="n">
-        <v>1134.950791002254</v>
+        <v>1054.520812792099</v>
       </c>
       <c r="U100" t="n">
-        <v>1080.405227774211</v>
+        <v>990.4095987901691</v>
       </c>
       <c r="V100" t="n">
-        <v>1027.788947830828</v>
+        <v>931.0818648639344</v>
       </c>
     </row>
     <row r="101">
@@ -8050,58 +8050,58 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1657.025082705157</v>
+        <v>5964.075961634261</v>
       </c>
       <c r="F101" t="n">
-        <v>1606.759514764726</v>
+        <v>5547.985673053945</v>
       </c>
       <c r="G101" t="n">
-        <v>1451.374119702066</v>
+        <v>4770.376148475114</v>
       </c>
       <c r="H101" t="n">
-        <v>1300.682124965135</v>
+        <v>4081.991504277654</v>
       </c>
       <c r="I101" t="n">
-        <v>1184.667779474462</v>
+        <v>3576.24741289451</v>
       </c>
       <c r="J101" t="n">
-        <v>1095.308048736498</v>
+        <v>3207.034274843963</v>
       </c>
       <c r="K101" t="n">
-        <v>1115.852014789339</v>
+        <v>2929.941382024663</v>
       </c>
       <c r="L101" t="n">
-        <v>1127.585462252073</v>
+        <v>2707.527621898264</v>
       </c>
       <c r="M101" t="n">
-        <v>1130.002353057648</v>
+        <v>2516.504724511719</v>
       </c>
       <c r="N101" t="n">
-        <v>1120.851277002105</v>
+        <v>2343.623424152996</v>
       </c>
       <c r="O101" t="n">
-        <v>1100.389902709748</v>
+        <v>2182.324995887441</v>
       </c>
       <c r="P101" t="n">
-        <v>1072.545712612655</v>
+        <v>2035.890741813212</v>
       </c>
       <c r="Q101" t="n">
-        <v>1042.026414816138</v>
+        <v>1905.255443764789</v>
       </c>
       <c r="R101" t="n">
-        <v>1008.175415861282</v>
+        <v>1783.404304252708</v>
       </c>
       <c r="S101" t="n">
-        <v>972.605722696049</v>
+        <v>1667.780408906952</v>
       </c>
       <c r="T101" t="n">
-        <v>934.723042987453</v>
+        <v>1558.687007770689</v>
       </c>
       <c r="U101" t="n">
-        <v>895.7642276827339</v>
+        <v>1457.127013800779</v>
       </c>
       <c r="V101" t="n">
-        <v>857.4751000457377</v>
+        <v>1363.506583076996</v>
       </c>
     </row>
     <row r="102">
@@ -8126,58 +8126,58 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1700.590289477204</v>
+        <v>3369.228693555275</v>
       </c>
       <c r="F102" t="n">
-        <v>1558.591965466699</v>
+        <v>3176.747846458302</v>
       </c>
       <c r="G102" t="n">
-        <v>1314.952554699338</v>
+        <v>2746.69579938714</v>
       </c>
       <c r="H102" t="n">
-        <v>1109.974038924957</v>
+        <v>2354.574297457102</v>
       </c>
       <c r="I102" t="n">
-        <v>964.2228413493663</v>
+        <v>2063.78425363176</v>
       </c>
       <c r="J102" t="n">
-        <v>860.7083650447971</v>
+        <v>1851.276608546821</v>
       </c>
       <c r="K102" t="n">
-        <v>854.2440897911006</v>
+        <v>1692.103374215323</v>
       </c>
       <c r="L102" t="n">
-        <v>845.8204706449808</v>
+        <v>1564.570145073592</v>
       </c>
       <c r="M102" t="n">
-        <v>834.6939677270916</v>
+        <v>1455.39319450443</v>
       </c>
       <c r="N102" t="n">
-        <v>819.9523062883097</v>
+        <v>1357.242446277139</v>
       </c>
       <c r="O102" t="n">
-        <v>800.2966984149514</v>
+        <v>1265.957292623188</v>
       </c>
       <c r="P102" t="n">
-        <v>779.2336400355008</v>
+        <v>1183.776343554037</v>
       </c>
       <c r="Q102" t="n">
-        <v>758.1258802856541</v>
+        <v>1110.834013949069</v>
       </c>
       <c r="R102" t="n">
-        <v>734.6885202335934</v>
+        <v>1042.603886422209</v>
       </c>
       <c r="S102" t="n">
-        <v>708.1510887481202</v>
+        <v>977.0460101064817</v>
       </c>
       <c r="T102" t="n">
-        <v>680.2685429244173</v>
+        <v>915.0405870373889</v>
       </c>
       <c r="U102" t="n">
-        <v>652.2632484851672</v>
+        <v>857.3660115702577</v>
       </c>
       <c r="V102" t="n">
-        <v>624.7653428969429</v>
+        <v>804.1250139011279</v>
       </c>
     </row>
     <row r="103">
@@ -8202,58 +8202,58 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1745.289969496961</v>
+        <v>3863.799964163366</v>
       </c>
       <c r="F103" t="n">
-        <v>1831.961988271352</v>
+        <v>3667.840806861033</v>
       </c>
       <c r="G103" t="n">
-        <v>1797.285744631372</v>
+        <v>3226.890101339809</v>
       </c>
       <c r="H103" t="n">
-        <v>1705.879454407497</v>
+        <v>2821.889638489649</v>
       </c>
       <c r="I103" t="n">
-        <v>1603.468051135471</v>
+        <v>2518.037081702468</v>
       </c>
       <c r="J103" t="n">
-        <v>1500.295531770532</v>
+        <v>2291.206615032189</v>
       </c>
       <c r="K103" t="n">
-        <v>1525.760309598989</v>
+        <v>2116.681432807369</v>
       </c>
       <c r="L103" t="n">
-        <v>1525.668783776101</v>
+        <v>1972.50876568135</v>
       </c>
       <c r="M103" t="n">
-        <v>1505.887470407109</v>
+        <v>1845.065149984638</v>
       </c>
       <c r="N103" t="n">
-        <v>1471.275489051028</v>
+        <v>1727.46563707702</v>
       </c>
       <c r="O103" t="n">
-        <v>1425.491461237146</v>
+        <v>1616.219854239016</v>
       </c>
       <c r="P103" t="n">
-        <v>1375.457814177782</v>
+        <v>1514.763902890453</v>
       </c>
       <c r="Q103" t="n">
-        <v>1324.02700966746</v>
+        <v>1423.596180602996</v>
       </c>
       <c r="R103" t="n">
-        <v>1267.845709731882</v>
+        <v>1337.122861882727</v>
       </c>
       <c r="S103" t="n">
-        <v>1207.547757993901</v>
+        <v>1253.265286530301</v>
       </c>
       <c r="T103" t="n">
-        <v>1146.410969213566</v>
+        <v>1173.566400826145</v>
       </c>
       <c r="U103" t="n">
-        <v>1087.34975112272</v>
+        <v>1099.525397496406</v>
       </c>
       <c r="V103" t="n">
-        <v>1029.608454629571</v>
+        <v>1030.743089543771</v>
       </c>
     </row>
     <row r="104">
@@ -8278,58 +8278,58 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>11912.87243249862</v>
+        <v>2306.171757421539</v>
       </c>
       <c r="F104" t="n">
-        <v>11031.99838709702</v>
+        <v>2225.054806861304</v>
       </c>
       <c r="G104" t="n">
-        <v>9423.032894724603</v>
+        <v>1955.298038813562</v>
       </c>
       <c r="H104" t="n">
-        <v>7911.958786780095</v>
+        <v>1692.017468219387</v>
       </c>
       <c r="I104" t="n">
-        <v>6787.171317249302</v>
+        <v>1491.62014308815</v>
       </c>
       <c r="J104" t="n">
-        <v>5970.593849897718</v>
+        <v>1343.511385639096</v>
       </c>
       <c r="K104" t="n">
-        <v>5012.537020968368</v>
+        <v>1232.410948853919</v>
       </c>
       <c r="L104" t="n">
-        <v>4296.899699884029</v>
+        <v>1143.662253959322</v>
       </c>
       <c r="M104" t="n">
-        <v>3736.627493527909</v>
+        <v>1067.783450447521</v>
       </c>
       <c r="N104" t="n">
-        <v>3281.773336523331</v>
+        <v>999.6668665120419</v>
       </c>
       <c r="O104" t="n">
-        <v>2903.960016452855</v>
+        <v>936.704779364371</v>
       </c>
       <c r="P104" t="n">
-        <v>2588.493004084104</v>
+        <v>880.1131497724956</v>
       </c>
       <c r="Q104" t="n">
-        <v>2326.562812648904</v>
+        <v>830.2895753244285</v>
       </c>
       <c r="R104" t="n">
-        <v>2100.41284447093</v>
+        <v>783.9154714242371</v>
       </c>
       <c r="S104" t="n">
-        <v>1898.505714959065</v>
+        <v>739.1178014961098</v>
       </c>
       <c r="T104" t="n">
-        <v>1716.014232051124</v>
+        <v>696.1390838989003</v>
       </c>
       <c r="U104" t="n">
-        <v>1551.325201370377</v>
+        <v>655.5580953720832</v>
       </c>
       <c r="V104" t="n">
-        <v>1404.13127646026</v>
+        <v>617.6849679020836</v>
       </c>
     </row>
     <row r="105">
@@ -8354,58 +8354,58 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1596.315942465461</v>
+        <v>2965.739592815615</v>
       </c>
       <c r="F105" t="n">
-        <v>1549.640280259329</v>
+        <v>2817.222352537549</v>
       </c>
       <c r="G105" t="n">
-        <v>1364.99139773449</v>
+        <v>2455.329083833819</v>
       </c>
       <c r="H105" t="n">
-        <v>1195.790495150471</v>
+        <v>2121.824736133055</v>
       </c>
       <c r="I105" t="n">
-        <v>1074.754816061272</v>
+        <v>1875.306774221131</v>
       </c>
       <c r="J105" t="n">
-        <v>992.0086922769805</v>
+        <v>1697.471879878336</v>
       </c>
       <c r="K105" t="n">
-        <v>1014.074979877035</v>
+        <v>1565.804021564399</v>
       </c>
       <c r="L105" t="n">
-        <v>1027.518378940271</v>
+        <v>1460.251254898387</v>
       </c>
       <c r="M105" t="n">
-        <v>1029.088093724472</v>
+        <v>1368.238666463775</v>
       </c>
       <c r="N105" t="n">
-        <v>1019.478630736964</v>
+        <v>1283.701099751068</v>
       </c>
       <c r="O105" t="n">
-        <v>1001.952945474944</v>
+        <v>1204.207347230582</v>
       </c>
       <c r="P105" t="n">
-        <v>982.5676006538487</v>
+        <v>1132.64490519765</v>
       </c>
       <c r="Q105" t="n">
-        <v>962.1349410968363</v>
+        <v>1068.999631288303</v>
       </c>
       <c r="R105" t="n">
-        <v>939.0366186007259</v>
+        <v>1009.346180118151</v>
       </c>
       <c r="S105" t="n">
-        <v>913.5185862057607</v>
+        <v>952.0519331427336</v>
       </c>
       <c r="T105" t="n">
-        <v>884.0821212203148</v>
+        <v>896.9796876637931</v>
       </c>
       <c r="U105" t="n">
-        <v>851.9294414392749</v>
+        <v>844.9121851262032</v>
       </c>
       <c r="V105" t="n">
-        <v>819.4755725581449</v>
+        <v>796.5139061377059</v>
       </c>
     </row>
     <row r="106">
@@ -8430,58 +8430,58 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1908.814103041096</v>
+        <v>3071.380295361185</v>
       </c>
       <c r="F106" t="n">
-        <v>1692.902581665115</v>
+        <v>2910.402111702184</v>
       </c>
       <c r="G106" t="n">
-        <v>1367.320438461662</v>
+        <v>2514.490334467237</v>
       </c>
       <c r="H106" t="n">
-        <v>1119.346322028334</v>
+        <v>2151.917989143082</v>
       </c>
       <c r="I106" t="n">
-        <v>955.3245005955922</v>
+        <v>1884.217300203791</v>
       </c>
       <c r="J106" t="n">
-        <v>846.4972641130696</v>
+        <v>1690.21461959458</v>
       </c>
       <c r="K106" t="n">
-        <v>839.5776201337629</v>
+        <v>1546.278326566218</v>
       </c>
       <c r="L106" t="n">
-        <v>834.6996820324365</v>
+        <v>1432.16851303878</v>
       </c>
       <c r="M106" t="n">
-        <v>827.8231720547736</v>
+        <v>1334.824650216174</v>
       </c>
       <c r="N106" t="n">
-        <v>816.7761160820924</v>
+        <v>1247.206838728408</v>
       </c>
       <c r="O106" t="n">
-        <v>800.3006789842179</v>
+        <v>1165.507299235326</v>
       </c>
       <c r="P106" t="n">
-        <v>782.1839814950985</v>
+        <v>1091.938397153148</v>
       </c>
       <c r="Q106" t="n">
-        <v>764.8216738442898</v>
+        <v>1026.989542085227</v>
       </c>
       <c r="R106" t="n">
-        <v>745.8395133316557</v>
+        <v>966.4715258853455</v>
       </c>
       <c r="S106" t="n">
-        <v>722.681518863617</v>
+        <v>907.9085977644901</v>
       </c>
       <c r="T106" t="n">
-        <v>696.1765861238558</v>
+        <v>851.8571414979201</v>
       </c>
       <c r="U106" t="n">
-        <v>667.6977677608941</v>
+        <v>799.1114656902238</v>
       </c>
       <c r="V106" t="n">
-        <v>638.9970022579027</v>
+        <v>750.1336776200382</v>
       </c>
     </row>
     <row r="107">
@@ -8506,58 +8506,58 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>537.2520392292751</v>
+        <v>2974.645603487354</v>
       </c>
       <c r="F107" t="n">
-        <v>479.5191866589713</v>
+        <v>2738.51422071679</v>
       </c>
       <c r="G107" t="n">
-        <v>421.5936970739732</v>
+        <v>2334.900840465939</v>
       </c>
       <c r="H107" t="n">
-        <v>372.9472794819739</v>
+        <v>1983.767677042387</v>
       </c>
       <c r="I107" t="n">
-        <v>335.7120685991818</v>
+        <v>1726.67593884887</v>
       </c>
       <c r="J107" t="n">
-        <v>306.3158882401111</v>
+        <v>1538.666841933349</v>
       </c>
       <c r="K107" t="n">
-        <v>307.6599853828347</v>
+        <v>1396.963915541404</v>
       </c>
       <c r="L107" t="n">
-        <v>306.5998946717261</v>
+        <v>1282.91201625786</v>
       </c>
       <c r="M107" t="n">
-        <v>303.7377385929802</v>
+        <v>1185.231857872474</v>
       </c>
       <c r="N107" t="n">
-        <v>299.4062390941843</v>
+        <v>1097.799072926234</v>
       </c>
       <c r="O107" t="n">
-        <v>293.6582747897424</v>
+        <v>1017.416878359444</v>
       </c>
       <c r="P107" t="n">
-        <v>287.4944461178736</v>
+        <v>945.4559386800145</v>
       </c>
       <c r="Q107" t="n">
-        <v>281.2677820567374</v>
+        <v>881.7871418633271</v>
       </c>
       <c r="R107" t="n">
-        <v>274.4769806545903</v>
+        <v>822.9014221983904</v>
       </c>
       <c r="S107" t="n">
-        <v>267.1506715255164</v>
+        <v>767.3779829800111</v>
       </c>
       <c r="T107" t="n">
-        <v>259.3821783064782</v>
+        <v>715.4343120071741</v>
       </c>
       <c r="U107" t="n">
-        <v>251.3194517777383</v>
+        <v>667.3667740512581</v>
       </c>
       <c r="V107" t="n">
-        <v>243.2177083843048</v>
+        <v>623.1953321972046</v>
       </c>
     </row>
     <row r="108">
@@ -8582,58 +8582,58 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1264.72871145863</v>
+        <v>3464.318827498281</v>
       </c>
       <c r="F108" t="n">
-        <v>1198.834328171699</v>
+        <v>3240.814983245362</v>
       </c>
       <c r="G108" t="n">
-        <v>1074.295330936108</v>
+        <v>2799.079448205199</v>
       </c>
       <c r="H108" t="n">
-        <v>957.2009411928594</v>
+        <v>2403.757456269552</v>
       </c>
       <c r="I108" t="n">
-        <v>867.2520964225977</v>
+        <v>2112.168313943484</v>
       </c>
       <c r="J108" t="n">
-        <v>796.6191904496952</v>
+        <v>1898.513474950127</v>
       </c>
       <c r="K108" t="n">
-        <v>805.409061941318</v>
+        <v>1737.599710737657</v>
       </c>
       <c r="L108" t="n">
-        <v>807.1550434888676</v>
+        <v>1607.917829542948</v>
       </c>
       <c r="M108" t="n">
-        <v>803.0765957694109</v>
+        <v>1496.361952004878</v>
       </c>
       <c r="N108" t="n">
-        <v>793.1218150619418</v>
+        <v>1395.611241417389</v>
       </c>
       <c r="O108" t="n">
-        <v>777.850314290298</v>
+        <v>1301.951172319386</v>
       </c>
       <c r="P108" t="n">
-        <v>759.5083339904251</v>
+        <v>1217.275467142367</v>
       </c>
       <c r="Q108" t="n">
-        <v>738.8730041290684</v>
+        <v>1141.512292865301</v>
       </c>
       <c r="R108" t="n">
-        <v>715.4687705956525</v>
+        <v>1070.548147457697</v>
       </c>
       <c r="S108" t="n">
-        <v>689.0822823763159</v>
+        <v>1002.468174826099</v>
       </c>
       <c r="T108" t="n">
-        <v>661.4440622631836</v>
+        <v>938.1455580335454</v>
       </c>
       <c r="U108" t="n">
-        <v>634.2151367381015</v>
+        <v>878.5076812583141</v>
       </c>
       <c r="V108" t="n">
-        <v>608.0472199283097</v>
+        <v>823.6700860136157</v>
       </c>
     </row>
     <row r="109">
@@ -8658,58 +8658,58 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>17285.90628475494</v>
+        <v>3413.754027781917</v>
       </c>
       <c r="F109" t="n">
-        <v>16111.86279054356</v>
+        <v>3292.6424531374</v>
       </c>
       <c r="G109" t="n">
-        <v>13202.74979872751</v>
+        <v>2872.924926963934</v>
       </c>
       <c r="H109" t="n">
-        <v>10540.13240767342</v>
+        <v>2461.226782275386</v>
       </c>
       <c r="I109" t="n">
-        <v>8587.446859996586</v>
+        <v>2145.728927345087</v>
       </c>
       <c r="J109" t="n">
-        <v>7254.678755938976</v>
+        <v>1913.942002198132</v>
       </c>
       <c r="K109" t="n">
-        <v>5915.148885800105</v>
+        <v>1741.456274130985</v>
       </c>
       <c r="L109" t="n">
-        <v>4973.26240538832</v>
+        <v>1605.380255761036</v>
       </c>
       <c r="M109" t="n">
-        <v>4273.297985443251</v>
+        <v>1490.79362106469</v>
       </c>
       <c r="N109" t="n">
-        <v>3724.8261143963</v>
+        <v>1389.186740324991</v>
       </c>
       <c r="O109" t="n">
-        <v>3277.184588341307</v>
+        <v>1295.947971858844</v>
       </c>
       <c r="P109" t="n">
-        <v>2909.00712837191</v>
+        <v>1212.600784404025</v>
       </c>
       <c r="Q109" t="n">
-        <v>2600.501492533155</v>
+        <v>1138.702039310249</v>
       </c>
       <c r="R109" t="n">
-        <v>2336.612264108298</v>
+        <v>1070.220196478729</v>
       </c>
       <c r="S109" t="n">
-        <v>2108.832453730824</v>
+        <v>1005.407180753886</v>
       </c>
       <c r="T109" t="n">
-        <v>1904.853908810801</v>
+        <v>943.8718935456758</v>
       </c>
       <c r="U109" t="n">
-        <v>1720.288961825484</v>
+        <v>885.9859951771371</v>
       </c>
       <c r="V109" t="n">
-        <v>1555.659401735367</v>
+        <v>832.2071157147875</v>
       </c>
     </row>
     <row r="110">
@@ -8734,58 +8734,58 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1457.507907433563</v>
+        <v>3969.748643876992</v>
       </c>
       <c r="F110" t="n">
-        <v>1328.689500160545</v>
+        <v>3705.492452704276</v>
       </c>
       <c r="G110" t="n">
-        <v>1119.762741989598</v>
+        <v>3182.896154860998</v>
       </c>
       <c r="H110" t="n">
-        <v>952.7899177380233</v>
+        <v>2717.584922783053</v>
       </c>
       <c r="I110" t="n">
-        <v>840.6076276955334</v>
+        <v>2376.615941474031</v>
       </c>
       <c r="J110" t="n">
-        <v>765.0635301430993</v>
+        <v>2129.41534523719</v>
       </c>
       <c r="K110" t="n">
-        <v>775.9065932511279</v>
+        <v>1945.631383166355</v>
       </c>
       <c r="L110" t="n">
-        <v>784.7065205082936</v>
+        <v>1799.175202646195</v>
       </c>
       <c r="M110" t="n">
-        <v>787.6280251351061</v>
+        <v>1673.566796619235</v>
       </c>
       <c r="N110" t="n">
-        <v>781.9005672018899</v>
+        <v>1559.654691536922</v>
       </c>
       <c r="O110" t="n">
-        <v>768.1536580765927</v>
+        <v>1453.232604475774</v>
       </c>
       <c r="P110" t="n">
-        <v>750.9434446510518</v>
+        <v>1357.081397532357</v>
       </c>
       <c r="Q110" t="n">
-        <v>733.187887978812</v>
+        <v>1271.770641126101</v>
       </c>
       <c r="R110" t="n">
-        <v>713.795004658342</v>
+        <v>1192.463586292388</v>
       </c>
       <c r="S110" t="n">
-        <v>691.4921081160311</v>
+        <v>1116.69838930316</v>
       </c>
       <c r="T110" t="n">
-        <v>666.9625212185889</v>
+        <v>1045.023700892455</v>
       </c>
       <c r="U110" t="n">
-        <v>641.739258050909</v>
+        <v>978.3472541035451</v>
       </c>
       <c r="V110" t="n">
-        <v>616.9672419784287</v>
+        <v>916.9328181372283</v>
       </c>
     </row>
     <row r="111">
@@ -8810,58 +8810,58 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>11769.22433735982</v>
+        <v>2635.772937843411</v>
       </c>
       <c r="F111" t="n">
-        <v>10795.80347311651</v>
+        <v>2520.537929646124</v>
       </c>
       <c r="G111" t="n">
-        <v>9202.34188962722</v>
+        <v>2202.34070168471</v>
       </c>
       <c r="H111" t="n">
-        <v>7861.339349268655</v>
+        <v>1904.337787991024</v>
       </c>
       <c r="I111" t="n">
-        <v>6891.297790641474</v>
+        <v>1681.363039770868</v>
       </c>
       <c r="J111" t="n">
-        <v>6194.049845171953</v>
+        <v>1518.208468482884</v>
       </c>
       <c r="K111" t="n">
-        <v>5294.31942810472</v>
+        <v>1396.090641961853</v>
       </c>
       <c r="L111" t="n">
-        <v>4598.076902937628</v>
+        <v>1297.96632603072</v>
       </c>
       <c r="M111" t="n">
-        <v>4027.834097428683</v>
+        <v>1212.84900716822</v>
       </c>
       <c r="N111" t="n">
-        <v>3550.148822748487</v>
+        <v>1135.543047846916</v>
       </c>
       <c r="O111" t="n">
-        <v>3146.750477669636</v>
+        <v>1063.642814403492</v>
       </c>
       <c r="P111" t="n">
-        <v>2813.244709571259</v>
+        <v>999.4282801080682</v>
       </c>
       <c r="Q111" t="n">
-        <v>2539.661397929818</v>
+        <v>943.3432185648528</v>
       </c>
       <c r="R111" t="n">
-        <v>2303.818267505263</v>
+        <v>891.3328864742149</v>
       </c>
       <c r="S111" t="n">
-        <v>2092.296809684512</v>
+        <v>841.1535326533237</v>
       </c>
       <c r="T111" t="n">
-        <v>1900.529579446443</v>
+        <v>793.1147704006116</v>
       </c>
       <c r="U111" t="n">
-        <v>1725.393801128671</v>
+        <v>747.6208725113944</v>
       </c>
       <c r="V111" t="n">
-        <v>1567.417939336549</v>
+        <v>705.0643287605634</v>
       </c>
     </row>
     <row r="112">
@@ -8886,58 +8886,58 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1551.765557411661</v>
+        <v>2543.268847812064</v>
       </c>
       <c r="F112" t="n">
-        <v>1416.746288017086</v>
+        <v>2414.88677092528</v>
       </c>
       <c r="G112" t="n">
-        <v>1182.689623230837</v>
+        <v>2095.072565460144</v>
       </c>
       <c r="H112" t="n">
-        <v>988.0209750092071</v>
+        <v>1799.081894764503</v>
       </c>
       <c r="I112" t="n">
-        <v>850.9388767089876</v>
+        <v>1578.655481573704</v>
       </c>
       <c r="J112" t="n">
-        <v>755.2649105371542</v>
+        <v>1417.718150973981</v>
       </c>
       <c r="K112" t="n">
-        <v>747.4906659547606</v>
+        <v>1297.650963556943</v>
       </c>
       <c r="L112" t="n">
-        <v>739.614191769683</v>
+        <v>1201.86928784297</v>
       </c>
       <c r="M112" t="n">
-        <v>729.2575775025114</v>
+        <v>1119.787199206995</v>
       </c>
       <c r="N112" t="n">
-        <v>714.3493771397918</v>
+        <v>1045.451807303294</v>
       </c>
       <c r="O112" t="n">
-        <v>695.1914401247792</v>
+        <v>976.0932671001203</v>
       </c>
       <c r="P112" t="n">
-        <v>674.9571141711285</v>
+        <v>913.5517142612887</v>
       </c>
       <c r="Q112" t="n">
-        <v>654.4883276596779</v>
+        <v>857.86386327028</v>
       </c>
       <c r="R112" t="n">
-        <v>632.7638892849701</v>
+        <v>805.8415335613005</v>
       </c>
       <c r="S112" t="n">
-        <v>609.6394174838201</v>
+        <v>756.0659025821052</v>
       </c>
       <c r="T112" t="n">
-        <v>585.2578497430213</v>
+        <v>708.8448131401645</v>
       </c>
       <c r="U112" t="n">
-        <v>560.8864406385197</v>
+        <v>664.8961979477958</v>
       </c>
       <c r="V112" t="n">
-        <v>537.1155296361592</v>
+        <v>624.330753362278</v>
       </c>
     </row>
     <row r="113">
@@ -9190,58 +9190,58 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>33081.25145734265</v>
+        <v>7004.39387524982</v>
       </c>
       <c r="F116" t="n">
-        <v>29268.97347601621</v>
+        <v>6697.904422100794</v>
       </c>
       <c r="G116" t="n">
-        <v>24593.12967567767</v>
+        <v>5879.736931737931</v>
       </c>
       <c r="H116" t="n">
-        <v>21586.3781510134</v>
+        <v>5281.252683870527</v>
       </c>
       <c r="I116" t="n">
-        <v>19716.48315109335</v>
+        <v>4864.612557353383</v>
       </c>
       <c r="J116" t="n">
-        <v>18434.60672623754</v>
+        <v>4548.546720535834</v>
       </c>
       <c r="K116" t="n">
-        <v>17401.52856136118</v>
+        <v>4279.841202662004</v>
       </c>
       <c r="L116" t="n">
-        <v>16369.44308516187</v>
+        <v>3932.807103944627</v>
       </c>
       <c r="M116" t="n">
-        <v>15308.0370418406</v>
+        <v>3571.162064997388</v>
       </c>
       <c r="N116" t="n">
-        <v>14181.27605224506</v>
+        <v>3239.33614259409</v>
       </c>
       <c r="O116" t="n">
-        <v>13035.54887120287</v>
+        <v>2948.030660896351</v>
       </c>
       <c r="P116" t="n">
-        <v>11957.34613493935</v>
+        <v>2691.44066240934</v>
       </c>
       <c r="Q116" t="n">
-        <v>10989.92338255495</v>
+        <v>2464.744136900123</v>
       </c>
       <c r="R116" t="n">
-        <v>10125.24215308837</v>
+        <v>2262.422667726796</v>
       </c>
       <c r="S116" t="n">
-        <v>9357.640141106183</v>
+        <v>2082.337251503073</v>
       </c>
       <c r="T116" t="n">
-        <v>8675.709300383933</v>
+        <v>1922.138397895854</v>
       </c>
       <c r="U116" t="n">
-        <v>8067.838292097194</v>
+        <v>1780.398791288987</v>
       </c>
       <c r="V116" t="n">
-        <v>7523.626276256273</v>
+        <v>1656.190113329043</v>
       </c>
     </row>
     <row r="117">
@@ -9266,58 +9266,58 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>18922.06470068057</v>
+        <v>4006.426246231721</v>
       </c>
       <c r="F117" t="n">
-        <v>16632.50259583943</v>
+        <v>3806.177650131064</v>
       </c>
       <c r="G117" t="n">
-        <v>13905.01096497607</v>
+        <v>3324.416517343656</v>
       </c>
       <c r="H117" t="n">
-        <v>12156.66923205542</v>
+        <v>2974.210938003294</v>
       </c>
       <c r="I117" t="n">
-        <v>11066.57899580143</v>
+        <v>2730.437205132799</v>
       </c>
       <c r="J117" t="n">
-        <v>10316.33290990571</v>
+        <v>2545.447425173445</v>
       </c>
       <c r="K117" t="n">
-        <v>9711.364729640352</v>
+        <v>2388.474021534486</v>
       </c>
       <c r="L117" t="n">
-        <v>9126.31638270425</v>
+        <v>2192.62449652227</v>
       </c>
       <c r="M117" t="n">
-        <v>8536.256242650405</v>
+        <v>1991.395394947638</v>
       </c>
       <c r="N117" t="n">
-        <v>7910.120781094042</v>
+        <v>1806.857157570376</v>
       </c>
       <c r="O117" t="n">
-        <v>7269.528470472849</v>
+        <v>1644.026886255228</v>
       </c>
       <c r="P117" t="n">
-        <v>6665.298688844873</v>
+        <v>1500.270688487042</v>
       </c>
       <c r="Q117" t="n">
-        <v>6123.432504088536</v>
+        <v>1373.321163106708</v>
       </c>
       <c r="R117" t="n">
-        <v>5639.590689559384</v>
+        <v>1260.131621534841</v>
       </c>
       <c r="S117" t="n">
-        <v>5209.814118422474</v>
+        <v>1159.329686611399</v>
       </c>
       <c r="T117" t="n">
-        <v>4827.571067495236</v>
+        <v>1069.567846969171</v>
       </c>
       <c r="U117" t="n">
-        <v>4486.679361175145</v>
+        <v>990.1138597882245</v>
       </c>
       <c r="V117" t="n">
-        <v>4180.508134753515</v>
+        <v>920.2631799069513</v>
       </c>
     </row>
     <row r="118">
@@ -9342,58 +9342,58 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>18920.80256954234</v>
+        <v>4006.159011362348</v>
       </c>
       <c r="F118" t="n">
-        <v>16632.73899381985</v>
+        <v>3806.23174738977</v>
       </c>
       <c r="G118" t="n">
-        <v>13918.56203096317</v>
+        <v>3327.656312532625</v>
       </c>
       <c r="H118" t="n">
-        <v>12180.83167823028</v>
+        <v>2980.122443067136</v>
       </c>
       <c r="I118" t="n">
-        <v>11097.78037765295</v>
+        <v>2738.135466169993</v>
       </c>
       <c r="J118" t="n">
-        <v>10352.97261362799</v>
+        <v>2554.487889479683</v>
       </c>
       <c r="K118" t="n">
-        <v>9752.963587475753</v>
+        <v>2398.705105843081</v>
       </c>
       <c r="L118" t="n">
-        <v>9172.070128611767</v>
+        <v>2203.616969257002</v>
       </c>
       <c r="M118" t="n">
-        <v>8584.609929498303</v>
+        <v>2002.675668938588</v>
       </c>
       <c r="N118" t="n">
-        <v>7958.78750807601</v>
+        <v>1817.973779731288</v>
       </c>
       <c r="O118" t="n">
-        <v>7316.514525785274</v>
+        <v>1654.652931465729</v>
       </c>
       <c r="P118" t="n">
-        <v>6709.602348973004</v>
+        <v>1510.242857139998</v>
       </c>
       <c r="Q118" t="n">
-        <v>6164.762605735905</v>
+        <v>1382.590392941772</v>
       </c>
       <c r="R118" t="n">
-        <v>5677.263676242251</v>
+        <v>1268.549417150972</v>
       </c>
       <c r="S118" t="n">
-        <v>5244.078595428736</v>
+        <v>1166.954493272416</v>
       </c>
       <c r="T118" t="n">
-        <v>4858.978593987595</v>
+        <v>1076.526311177267</v>
       </c>
       <c r="U118" t="n">
-        <v>4514.751696407073</v>
+        <v>996.3088217935249</v>
       </c>
       <c r="V118" t="n">
-        <v>4205.662701370411</v>
+        <v>925.8005023365478</v>
       </c>
     </row>
     <row r="119">
@@ -9418,58 +9418,58 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>20027.97775526549</v>
+        <v>4240.584577147039</v>
       </c>
       <c r="F119" t="n">
-        <v>17624.78529250788</v>
+        <v>4033.25136925938</v>
       </c>
       <c r="G119" t="n">
-        <v>14729.60880481466</v>
+        <v>3521.56175410298</v>
       </c>
       <c r="H119" t="n">
-        <v>12866.20023058874</v>
+        <v>3147.802471701501</v>
       </c>
       <c r="I119" t="n">
-        <v>11701.91630837783</v>
+        <v>2887.192841795127</v>
       </c>
       <c r="J119" t="n">
-        <v>10900.73418773909</v>
+        <v>2689.642338312502</v>
       </c>
       <c r="K119" t="n">
-        <v>10256.6716963353</v>
+        <v>2522.590241039741</v>
       </c>
       <c r="L119" t="n">
-        <v>9636.391526085452</v>
+        <v>2315.171557950667</v>
       </c>
       <c r="M119" t="n">
-        <v>9011.659999238322</v>
+        <v>2102.300787741329</v>
       </c>
       <c r="N119" t="n">
-        <v>8348.483058986631</v>
+        <v>1906.989385802769</v>
       </c>
       <c r="O119" t="n">
-        <v>7669.354005165018</v>
+        <v>1734.448697175608</v>
       </c>
       <c r="P119" t="n">
-        <v>7028.896483794495</v>
+        <v>1582.111749120728</v>
       </c>
       <c r="Q119" t="n">
-        <v>6454.913491151088</v>
+        <v>1447.663430184381</v>
       </c>
       <c r="R119" t="n">
-        <v>5942.646155232494</v>
+        <v>1327.84748894146</v>
       </c>
       <c r="S119" t="n">
-        <v>5488.34965764545</v>
+        <v>1221.311652190567</v>
       </c>
       <c r="T119" t="n">
-        <v>5084.12332744102</v>
+        <v>1126.408035232951</v>
       </c>
       <c r="U119" t="n">
-        <v>4722.849844131777</v>
+        <v>1042.231617621157</v>
       </c>
       <c r="V119" t="n">
-        <v>4399.47691817469</v>
+        <v>968.4651932601428</v>
       </c>
     </row>
     <row r="120">
@@ -9494,58 +9494,58 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>20274.5216663023</v>
+        <v>4292.786068514069</v>
       </c>
       <c r="F120" t="n">
-        <v>17859.11727561725</v>
+        <v>4086.875840529547</v>
       </c>
       <c r="G120" t="n">
-        <v>14955.84436246176</v>
+        <v>3575.65025694427</v>
       </c>
       <c r="H120" t="n">
-        <v>13090.68723053391</v>
+        <v>3202.724726974599</v>
       </c>
       <c r="I120" t="n">
-        <v>11926.48500823726</v>
+        <v>2942.60027470913</v>
       </c>
       <c r="J120" t="n">
-        <v>11124.45211858953</v>
+        <v>2744.842401761751</v>
       </c>
       <c r="K120" t="n">
-        <v>10476.93477476766</v>
+        <v>2576.763125618815</v>
       </c>
       <c r="L120" t="n">
-        <v>9838.330458929566</v>
+        <v>2363.687983659552</v>
       </c>
       <c r="M120" t="n">
-        <v>9187.980956374508</v>
+        <v>2143.434129118308</v>
       </c>
       <c r="N120" t="n">
-        <v>8500.924851104308</v>
+        <v>1941.810667394612</v>
       </c>
       <c r="O120" t="n">
-        <v>7803.756783068528</v>
+        <v>1764.844311073367</v>
       </c>
       <c r="P120" t="n">
-        <v>7148.798626070854</v>
+        <v>1609.100137486216</v>
       </c>
       <c r="Q120" t="n">
-        <v>6562.041366754681</v>
+        <v>1471.689330465421</v>
       </c>
       <c r="R120" t="n">
-        <v>6038.254283513398</v>
+        <v>1349.210533233031</v>
       </c>
       <c r="S120" t="n">
-        <v>5573.55791166519</v>
+        <v>1240.272877335981</v>
       </c>
       <c r="T120" t="n">
-        <v>5160.719155575408</v>
+        <v>1143.378149992996</v>
       </c>
       <c r="U120" t="n">
-        <v>4792.531373366905</v>
+        <v>1057.608835886941</v>
       </c>
       <c r="V120" t="n">
-        <v>4462.869672815132</v>
+        <v>982.4199605029642</v>
       </c>
     </row>
     <row r="121">
@@ -9570,58 +9570,58 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>17316.22068019792</v>
+        <v>3666.41601304766</v>
       </c>
       <c r="F121" t="n">
-        <v>15244.02046218641</v>
+        <v>3488.437752956002</v>
       </c>
       <c r="G121" t="n">
-        <v>12741.80815248977</v>
+        <v>3046.317445535797</v>
       </c>
       <c r="H121" t="n">
-        <v>11134.51428053919</v>
+        <v>2724.133850351311</v>
       </c>
       <c r="I121" t="n">
-        <v>10135.3473022868</v>
+        <v>2500.67607809112</v>
       </c>
       <c r="J121" t="n">
-        <v>9452.9046814514</v>
+        <v>2332.405525485634</v>
       </c>
       <c r="K121" t="n">
-        <v>8907.469517388578</v>
+        <v>2190.758985189159</v>
       </c>
       <c r="L121" t="n">
-        <v>8381.219751526396</v>
+        <v>2013.61282770381</v>
       </c>
       <c r="M121" t="n">
-        <v>7848.288185528236</v>
+        <v>1830.901569328774</v>
       </c>
       <c r="N121" t="n">
-        <v>7279.077751235941</v>
+        <v>1662.712125303211</v>
       </c>
       <c r="O121" t="n">
-        <v>6693.564576750723</v>
+        <v>1513.770827602905</v>
       </c>
       <c r="P121" t="n">
-        <v>6139.694220877213</v>
+        <v>1381.964065803136</v>
       </c>
       <c r="Q121" t="n">
-        <v>5642.209045610835</v>
+        <v>1265.395688417816</v>
       </c>
       <c r="R121" t="n">
-        <v>5197.56046859045</v>
+        <v>1161.362705525675</v>
       </c>
       <c r="S121" t="n">
-        <v>4802.864278241967</v>
+        <v>1068.771939259578</v>
       </c>
       <c r="T121" t="n">
-        <v>4451.542890313836</v>
+        <v>986.2572872198256</v>
       </c>
       <c r="U121" t="n">
-        <v>4137.26885508595</v>
+        <v>913.0064587465013</v>
       </c>
       <c r="V121" t="n">
-        <v>3855.856021482829</v>
+        <v>848.7968948296908</v>
       </c>
     </row>
     <row r="122">
@@ -9646,58 +9646,58 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>315.3904933978865</v>
+        <v>4948.069849856294</v>
       </c>
       <c r="F122" t="n">
-        <v>501.3653455410364</v>
+        <v>4707.085680859978</v>
       </c>
       <c r="G122" t="n">
-        <v>565.7539350161853</v>
+        <v>4116.465169306185</v>
       </c>
       <c r="H122" t="n">
-        <v>601.8303364967546</v>
+        <v>3685.724862194558</v>
       </c>
       <c r="I122" t="n">
-        <v>634.5854513872886</v>
+        <v>3384.809156558133</v>
       </c>
       <c r="J122" t="n">
-        <v>665.9616395094544</v>
+        <v>3155.527113611061</v>
       </c>
       <c r="K122" t="n">
-        <v>692.8355489271655</v>
+        <v>2960.356195255283</v>
       </c>
       <c r="L122" t="n">
-        <v>692.5906296907153</v>
+        <v>2713.221203852336</v>
       </c>
       <c r="M122" t="n">
-        <v>674.386313714993</v>
+        <v>2458.227141579636</v>
       </c>
       <c r="N122" t="n">
-        <v>648.6612469961676</v>
+        <v>2225.293590940485</v>
       </c>
       <c r="O122" t="n">
-        <v>621.2253149541684</v>
+        <v>2021.230453719267</v>
       </c>
       <c r="P122" t="n">
-        <v>593.512025831805</v>
+        <v>1841.858078712661</v>
       </c>
       <c r="Q122" t="n">
-        <v>566.5473899068791</v>
+        <v>1683.718222670271</v>
       </c>
       <c r="R122" t="n">
-        <v>540.8659436420191</v>
+        <v>1542.846056714064</v>
       </c>
       <c r="S122" t="n">
-        <v>517.4228416488768</v>
+        <v>1417.597265535941</v>
       </c>
       <c r="T122" t="n">
-        <v>496.784016057827</v>
+        <v>1306.231334604019</v>
       </c>
       <c r="U122" t="n">
-        <v>479.0900615308726</v>
+        <v>1207.677785660951</v>
       </c>
       <c r="V122" t="n">
-        <v>463.4295852536197</v>
+        <v>1121.288638285296</v>
       </c>
     </row>
     <row r="123">
@@ -9722,58 +9722,58 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5777.564733221379</v>
+        <v>10465.08259319663</v>
       </c>
       <c r="F123" t="n">
-        <v>5477.799737025253</v>
+        <v>9659.986912590026</v>
       </c>
       <c r="G123" t="n">
-        <v>4791.194366460662</v>
+        <v>8491.84100465853</v>
       </c>
       <c r="H123" t="n">
-        <v>4166.184070060909</v>
+        <v>7425.444401941775</v>
       </c>
       <c r="I123" t="n">
-        <v>3655.293757424326</v>
+        <v>6554.59031478394</v>
       </c>
       <c r="J123" t="n">
-        <v>3259.188095699836</v>
+        <v>5870.892330088866</v>
       </c>
       <c r="K123" t="n">
-        <v>2945.739361352345</v>
+        <v>5317.33249477808</v>
       </c>
       <c r="L123" t="n">
-        <v>2687.563218455734</v>
+        <v>4859.366332070833</v>
       </c>
       <c r="M123" t="n">
-        <v>2459.642658317629</v>
+        <v>4455.601291191821</v>
       </c>
       <c r="N123" t="n">
-        <v>2257.276390109839</v>
+        <v>4093.516886312319</v>
       </c>
       <c r="O123" t="n">
-        <v>2072.497382828436</v>
+        <v>3751.758362341766</v>
       </c>
       <c r="P123" t="n">
-        <v>1913.252198441702</v>
+        <v>3447.05042079189</v>
       </c>
       <c r="Q123" t="n">
-        <v>1775.726836024069</v>
+        <v>3174.226255188731</v>
       </c>
       <c r="R123" t="n">
-        <v>1653.538048575382</v>
+        <v>2926.408522827177</v>
       </c>
       <c r="S123" t="n">
-        <v>1542.385804738095</v>
+        <v>2698.434740548167</v>
       </c>
       <c r="T123" t="n">
-        <v>1441.855383587751</v>
+        <v>2490.738017101241</v>
       </c>
       <c r="U123" t="n">
-        <v>1349.586236169403</v>
+        <v>2300.801314239769</v>
       </c>
       <c r="V123" t="n">
-        <v>1266.302148862313</v>
+        <v>2129.264519466805</v>
       </c>
     </row>
     <row r="124">
@@ -9798,58 +9798,58 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2912.808347369382</v>
+        <v>3776.721998085051</v>
       </c>
       <c r="F124" t="n">
-        <v>2747.595091534997</v>
+        <v>3580.34426433088</v>
       </c>
       <c r="G124" t="n">
-        <v>2447.159053115874</v>
+        <v>3215.550132804394</v>
       </c>
       <c r="H124" t="n">
-        <v>2181.533038612824</v>
+        <v>2865.891929253758</v>
       </c>
       <c r="I124" t="n">
-        <v>1975.377105951276</v>
+        <v>2576.919700201208</v>
       </c>
       <c r="J124" t="n">
-        <v>1822.21670033934</v>
+        <v>2350.812973427494</v>
       </c>
       <c r="K124" t="n">
-        <v>1702.311241059009</v>
+        <v>2168.050859934016</v>
       </c>
       <c r="L124" t="n">
-        <v>1605.805485846893</v>
+        <v>2017.811677609164</v>
       </c>
       <c r="M124" t="n">
-        <v>1519.8114609371</v>
+        <v>1884.37119959046</v>
       </c>
       <c r="N124" t="n">
-        <v>1439.24021041086</v>
+        <v>1762.305053330895</v>
       </c>
       <c r="O124" t="n">
-        <v>1356.928664053013</v>
+        <v>1642.032321815639</v>
       </c>
       <c r="P124" t="n">
-        <v>1278.400576954631</v>
+        <v>1531.336091680631</v>
       </c>
       <c r="Q124" t="n">
-        <v>1204.0393310349</v>
+        <v>1429.540953437886</v>
       </c>
       <c r="R124" t="n">
-        <v>1134.76270791064</v>
+        <v>1335.32265177944</v>
       </c>
       <c r="S124" t="n">
-        <v>1067.593047095128</v>
+        <v>1246.151984073008</v>
       </c>
       <c r="T124" t="n">
-        <v>1003.829686127816</v>
+        <v>1163.148766134306</v>
       </c>
       <c r="U124" t="n">
-        <v>943.7256947466992</v>
+        <v>1086.054086084788</v>
       </c>
       <c r="V124" t="n">
-        <v>888.29035002116</v>
+        <v>1015.660628480093</v>
       </c>
     </row>
     <row r="125">
@@ -9874,58 +9874,58 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3918.349170690647</v>
+        <v>2991.914301388462</v>
       </c>
       <c r="F125" t="n">
-        <v>3935.559874834406</v>
+        <v>2980.512571257519</v>
       </c>
       <c r="G125" t="n">
-        <v>3772.40065502044</v>
+        <v>2811.413812408071</v>
       </c>
       <c r="H125" t="n">
-        <v>3531.56721313342</v>
+        <v>2613.271833945194</v>
       </c>
       <c r="I125" t="n">
-        <v>3281.702330500445</v>
+        <v>2429.654236770864</v>
       </c>
       <c r="J125" t="n">
-        <v>3054.49375177771</v>
+        <v>2274.068840661626</v>
       </c>
       <c r="K125" t="n">
-        <v>2850.162960824353</v>
+        <v>2139.155615799025</v>
       </c>
       <c r="L125" t="n">
-        <v>2671.003903153372</v>
+        <v>2022.587430941509</v>
       </c>
       <c r="M125" t="n">
-        <v>2504.570661377191</v>
+        <v>1913.195908788593</v>
       </c>
       <c r="N125" t="n">
-        <v>2349.01758739825</v>
+        <v>1808.666662476546</v>
       </c>
       <c r="O125" t="n">
-        <v>2191.93035439599</v>
+        <v>1699.611111635566</v>
       </c>
       <c r="P125" t="n">
-        <v>2048.671146899979</v>
+        <v>1597.805747158425</v>
       </c>
       <c r="Q125" t="n">
-        <v>1917.552671062001</v>
+        <v>1503.384380974065</v>
       </c>
       <c r="R125" t="n">
-        <v>1791.556801892369</v>
+        <v>1412.439260566359</v>
       </c>
       <c r="S125" t="n">
-        <v>1670.645946103637</v>
+        <v>1324.262322259368</v>
       </c>
       <c r="T125" t="n">
-        <v>1557.267308838537</v>
+        <v>1240.976391337676</v>
       </c>
       <c r="U125" t="n">
-        <v>1451.182639406108</v>
+        <v>1162.621205782519</v>
       </c>
       <c r="V125" t="n">
-        <v>1353.414736684361</v>
+        <v>1090.22340840938</v>
       </c>
     </row>
     <row r="126">
